--- a/important_mails_2026-08-04.xlsx
+++ b/important_mails_2026-08-04.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H287"/>
+  <dimension ref="A1:H288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -548,21 +548,70 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tue, 4 Aug 2026 05:41:28 +0000</t>
+          <t>Tue, 4 Aug 2026 12:59:47 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Dein Einkaufswagen wartet</t>
+          <t>Tu pago está en camino</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 08/04/26 12:59 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 371,43.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 4 Aug 2026 05:41:28 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 145 PCS Eisenbahn Elektrisch Cube Track, 3D Schwerkrafttrotzendes Zug Set, DIY Zugstrecken Spielzeug, STEM Lernspielzeug &amp;amp; Geschenkidee für Kinder 3–8 Jahre, Kreatives Bauen Spielzeug
@@ -577,39 +626,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 16:27:49 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (3rwPw0NlBZ)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -629,39 +678,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 04:52:33 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -677,39 +726,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 04:46:25 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -725,39 +774,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 04:49:15 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -773,39 +822,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 09:23:20 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -821,39 +870,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 19:42:31 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (YsvR7aqoWy)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -878,39 +927,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 07:19:03 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (8AOhKJjKS4)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -930,39 +979,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 05:45:50 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -978,39 +1027,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:56:25 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Amazon.sa" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been successfully updated</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been successfully updated
@@ -1026,39 +1075,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:49:41 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Amazon.fr" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Account Protection</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon Seller Account Protection
@@ -1075,39 +1124,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:48:37 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"Amazon.ae" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been successfully updated</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been successfully updated
@@ -1123,39 +1172,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:43:00 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -1171,39 +1220,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:38:29 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -1219,39 +1268,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 14:56:26 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1272,39 +1321,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 05:51:10 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1317,63 +1366,6 @@
 - In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
 - To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
 -</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 28 Jul 2026 09:53:48 +0000</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (WXuXOpUPId)</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 1
-Quantity Successfully Destroyed: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-8893641-4969855
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-457399073370325</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1769,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1792,7 +1784,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Tue, 28 Jul 2026 14:44:59 +0000</t>
+          <t>Mon, 3 Aug 2026 17:55:58 +0000</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1802,271 +1794,11 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Tu pago está en camino</t>
+          <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 07/28/26 14:44 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 382,74.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 28 Jul 2026 14:36:09 +0000</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 07/28/26 14:35 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 246.34.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 28 Jul 2026 13:50:18 +0000</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Your information is verified – Start selling on Amazon now</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>96
- Dear Seller,
-Good news. Your Selling on Amazon payment account has been activated. We will get in touch with you if we need more information.
- For any assistance relating to Selling on Amazon or other Amazon services, you can search our help pages or contact Seller Support/Selling Partner Support.
-Happy Selling.
-Amazon Payments
- Please Note: this email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions, visit: Seller Central
- To change your email preferences, visit: Notification Preferences
- Copyright 2026 Amazon, Inc or its affiliates. All rights reserved.
- Amazon Payments UK Limited, a private company limited by shares,
-is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60)
-with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom.
-Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority
-under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
-Amazon Payments is a trading name of Amazon Payments UK Lim</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 28 Jul 2026 12:05:03 +0000</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Airline discounts and $100 off registration. Available for a limited
- time</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-20/7z4slz6/6793898954/h/insOo6D5kr2g-YQAHmot70JWv4JNrnk-FJT9rhAtCXc)
-[Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4slz9/6793898954/h/insOo6D5kr2g-YQAHmot70JWv4JNrnk-FJT9rhAtCXc)
-We want you there—so we made it easier
-Your travel plans start here, with exclusive discounts to help make your trip to Seattle more affordable.
-Register now to get the early-bird rate, and join us in Seattle from September 22 to 24. Seats are limited, secure yours today!
-[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4slz9/6793898954/h/insOo6D5kr2g-YQAHmot70JWv4JNrnk-FJT9rhAtCXc)
-"Attending Amazon Accelerate for the first time has been an amazing experience! I feel inspired and more confident in my ability to grow my business with Amazon."
-2025 attendee
-Save on your flight to Seattle
-We’ve partnered with major airlines to offer exclusive discounts on flights to and from Seattle-Tacoma International Airport (SEA).
-[A checkmark icon]
-Alaska Airlines: ~7% off the published price of select fares | Code: ECMQ023 | Valid Sept 17–29
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 28 Jul 2026 08:56:50 +0000</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Your information is verified – Start selling on Amazon now</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>96
- Dear Seller,
-Good news. Your Selling on Amazon payment account has been activated. We will get in touch with you if we need more information.
- For any assistance relating to Selling on Amazon or other Amazon services, you can search our help pages or contact Seller Support/Selling Partner Support.
-Happy Selling.
-Amazon Payments
- Please Note: this email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions, visit: Seller Central
- To change your email preferences, visit: Notification Preferences
- Copyright 2026 Amazon, Inc or its affiliates. All rights reserved.
- Amazon Payments UK Limited, a private company limited by shares,
-is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60)
-with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom.
-Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority
-under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
-Amazon Payments is a trading name of Amazon Payments UK Lim</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 3 Aug 2026 17:55:58 +0000</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2085,39 +1817,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:41:59 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2136,39 +1868,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 15:45:25 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -2195,39 +1927,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 09:15:08 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2245,39 +1977,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 03:48:43 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -2305,39 +2037,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 00:32:40 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2355,39 +2087,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 00:25:49 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2405,39 +2137,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 16:15:51 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2455,39 +2187,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 15:08:44 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Hello xiao jianming,
@@ -2506,39 +2238,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 15:08:23 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello xiao jianming,
@@ -2554,39 +2286,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:23:21 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2604,39 +2336,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:17:26 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2654,39 +2386,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2702,39 +2434,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:10:39 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Action required: Notification of ASIN removal</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -2750,40 +2482,40 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 09:26:45 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.de" &lt;toys-safety-mv@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13104358872] SELLER: A1UYGOR4ZW45MU, ASIN: B0F13M1H6F,
  MARKETPLACE: 4 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13104358872] SELLER: A1UYGOR4ZW45MU, ASIN: B0F13M1H6F, MARKETPLACE: 4 - PS - APPEAL
@@ -2808,39 +2540,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:42:30 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -2858,40 +2590,40 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:41:59 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -2909,39 +2641,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:41:27 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -2958,39 +2690,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:28:39 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -3008,39 +2740,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:16:39 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -3079,40 +2811,40 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:06:40 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -3130,39 +2862,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 17:06:20 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -3180,39 +2912,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mon, 3 Aug 2026 10:36:14 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>通过 Q4 活动拓展您的业务 — 尽早提报，节省费用</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Q4 业绩
 尊敬的卖家，
@@ -3242,39 +2974,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 13:53:08 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3289,39 +3021,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 10:56:43 +0200</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"poststelle@fa15.berlin.de" &lt;poststelle@fa15.berlin.de&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>automatische Eingangsbestätigung - bitte nicht antworten</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Guten Tag,
 vielen Dank für Ihre Nachricht. Dies ist eine automatisch erzeugte Eingangsbestätigung.
@@ -3335,39 +3067,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 00:19:33 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -3383,40 +3115,40 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sun, 2 Aug 2026 00:19:03 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -3432,39 +3164,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 23:42:26 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -3480,39 +3212,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 23:41:49 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -3551,40 +3283,40 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 23:41:18 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -3600,39 +3332,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 02:59:47 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 07/2026</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -3650,39 +3382,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:19:56 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Toma medidas: notificación de retirada de ASIN</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -3696,40 +3428,40 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:18:06 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -3745,39 +3477,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:18:01 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -3791,39 +3523,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:17:18 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -3839,39 +3571,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:13:36 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Åtgärd krävs: Meddelande om borttagning av ASIN</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hej Weihai EU!
@@ -3886,39 +3618,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:12:04 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Azione richiesta: notifica di rimozione ASIN</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -3933,39 +3665,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:11:55 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -3981,39 +3713,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 23:32:42 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -4029,40 +3761,40 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 23:27:07 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -4078,39 +3810,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 07:22:18 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4129,39 +3861,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 07:18:49 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 145 PCS Eisenbahn Elektrisch Cube Track, 3D Schwerkrafttrotzendes Zug Set, DIY Zugstrecken Spielzeug, STEM Lernspielzeug &amp;amp; Geschenkidee für Kinder 3–8 Jahre, Kreatives Bauen Spielzeug
@@ -4183,40 +3915,40 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 04:16:04 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Soluciona los errores de precio para restablecer los listings
  desactivados.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Eliminar errores de precio
@@ -4237,39 +3969,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 04:16:02 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Powiadomienia Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Rozwiąż błędy w obrębie cen, aby umożliwić ponowną aktywację ofert</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Zatrzymanie spowodowane błędem ceny
@@ -4290,39 +4022,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:57:33 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"Amazon.pl" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Informacje o Twoim koncie bankowym Amazon zostały pomyślnie zaktualizowane</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Informacje o Twoim koncie bankowym Amazon zostały pomyślnie zaktualizowane
@@ -4335,39 +4067,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:47:43 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Amazon.es" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>La información de tu cuenta bancaria de Amazon se ha actualizado correctamente</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  La información de tu cuenta bancaria de Amazon se ha actualizado correctamente
@@ -4380,39 +4112,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:45:55 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"Amazon.es" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>La información de tu cuenta bancaria de Amazon se ha actualizado correctamente</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  La información de tu cuenta bancaria de Amazon se ha actualizado correctamente
@@ -4425,39 +4157,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 11:26:20 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Ukończ rejestrację opakowań UE według kraju</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Ukończ rejestrację opakowań UE według kraju
  96
@@ -4467,39 +4199,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 17:52:28 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Presentar información de cumplimiento normativo de la RAP en Portugal</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  La normativa portuguesa sobre la RAP se aplica a los productos vendidos a clientes de Portugal.
@@ -4516,39 +4248,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 04:26:40 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-08-13</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -4572,39 +4304,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 03:08:11 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -4628,39 +4360,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sat, 1 Aug 2026 00:17:46 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>View your US Q3-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q3-2026
@@ -4690,88 +4422,96 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 28 Jul 2026 14:32:02 +0000</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>Add WhatsApp to your notification preferences</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>96
- Stay connected with account updates on WhatsApp—opt in today to get started
- Hello,
- We're excited to share a new communication channel for your Amazon US selling account. You can now choose to receive important updates, notifications, and support via WhatsApp , giving you more flexibility in how you stay informed.
- What this means for you
- WhatsApp is now available as an additional channel for receiving alerts about your Amazon US selling account. This is entirely optional — you won't receive any WhatsApp messages unless you choose to opt in. You'll continue to use Seller Central as the primary way to manage your orders and account.
- Update preferences
- How to opt in If you'd like to receive notifications via WhatsApp, follow these steps:
-- Visit the Notification Preferences page in Seller Central
-- Navigate to the WhatsApp tab
-- Add your mobile phone number and complete the verification process Once verified, you'll begin receiving notifications to that number. You can update your preferences at any time, and enabling WhatsApp will not affect your other communication channels with Amazon Seller Services.
- If you opt in and later change your mind, you can opt out at any time b</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 09:53:48 +0000</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (WXuXOpUPId)</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 1
+Quantity Successfully Destroyed: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-8893641-4969855
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-457399073370325</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 06:03:52 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4787,39 +4527,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 16:41:05 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (ckaicj9NPD)</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4839,39 +4579,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 09:48:04 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4887,39 +4627,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 04:57:36 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4935,39 +4675,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Jul 2026 20:49:44 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (1pqaY5uvK2)</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4992,39 +4732,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Jul 2026 14:44:02 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $63.02 in an attempt to settle your Amazon seller account balance.
@@ -5040,39 +4780,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Jul 2026 04:57:25 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5088,39 +4828,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 05:07:54 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5136,39 +4876,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 16:10:45 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -5184,39 +4924,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 10:35:17 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Zx1U3/hDuM)</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5236,39 +4976,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 05:01:14 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5284,39 +5024,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 05:03:32 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5332,39 +5072,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 09:30:25 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5380,39 +5120,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 04:57:37 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5428,39 +5168,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 14:04:25 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -5481,39 +5221,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 04:59:54 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5529,39 +5269,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Jul 2026 14:58:02 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -5582,39 +5322,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Jul 2026 05:03:59 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5630,39 +5370,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 05:02:32 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5678,39 +5418,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Wed, 15 Jul 2026 04:56:43 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5726,39 +5466,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 15:08:13 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -5779,39 +5519,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 04:45:43 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5827,39 +5567,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Jul 2026 14:23:23 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $88.37 in an attempt to settle your Amazon seller account balance.
@@ -5875,39 +5615,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 09:58:04 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5923,39 +5663,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 05:37:52 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -5971,39 +5711,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 05:20:26 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6019,39 +5759,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 03:39:42 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6067,39 +5807,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 05:28:59 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0uWEj59btv)</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -6119,39 +5859,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 04:32:11 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -6167,39 +5907,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Jul 2026 06:15:19 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>【官方提示】请尽快通过您的欧洲站卖家资质KYC审核，以保证正常销售</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">账户注册
 															资质审查
@@ -6232,40 +5972,40 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 11:09:39 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Verstrek KYC-verificatie binnen 45 dagen om beperkingen te
  voorkomen</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Verstrek KYC-verificatie binnen 45 dagen om beperkingen te voorkomen
@@ -6284,39 +6024,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 10:52:41 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Provide KYC verification within 45 days to avoid restrictions</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Provide KYC verification within 45 days to avoid restrictions
@@ -6335,39 +6075,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 09:42:14 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Provide KYC verification within 45 days to avoid restrictions</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Provide KYC verification within 45 days to avoid restrictions
@@ -6386,39 +6126,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 09:24:08 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Fournissez une vérification KYC sous 45 jours pour éviter les restrictions</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Fournissez une vérification KYC sous 45 jours pour éviter les restrictions
@@ -6434,39 +6174,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 08:07:04 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -6483,39 +6223,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 07:52:22 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -6553,39 +6293,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Jul 2026 08:31:05 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -6602,39 +6342,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Jul 2026 08:30:30 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -6672,39 +6412,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 16:00:40 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -6721,39 +6461,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 15:59:18 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -6791,39 +6531,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 07:44:38 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -6840,40 +6580,40 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 07:43:19 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Information needed for your Selling on Amazon
  payment account</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 [Action Required] Information needed for your Selling on Amazon payment account
@@ -6888,39 +6628,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 06:09:58 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>【官方提示】请尽快通过您的欧洲站卖家资质KYC审核，以保证正常销售</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">账户注册
 															资质审查
@@ -6953,39 +6693,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 08:27:01 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -7002,40 +6742,40 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 08:25:53 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Information needed for your Selling on Amazon
  payment account</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 [Action Required] Information needed for your Selling on Amazon payment account
@@ -7050,39 +6790,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:11:12 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -7096,6 +6836,266 @@
  We’re here to help.
  If you have any questions, you can contact us at any time via Amazon Selling Partner Support .
  For more informa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 14:44:59 +0000</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 07/28/26 14:44 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 382,74.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 14:36:09 +0000</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement attempted
+Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
+On 07/28/26 14:35 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
+ 246.34.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon Store,
+Amazon Services
+Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 13:50:18 +0000</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Your information is verified – Start selling on Amazon now</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Dear Seller,
+Good news. Your Selling on Amazon payment account has been activated. We will get in touch with you if we need more information.
+ For any assistance relating to Selling on Amazon or other Amazon services, you can search our help pages or contact Seller Support/Selling Partner Support.
+Happy Selling.
+Amazon Payments
+ Please Note: this email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions, visit: Seller Central
+ To change your email preferences, visit: Notification Preferences
+ Copyright 2026 Amazon, Inc or its affiliates. All rights reserved.
+ Amazon Payments UK Limited, a private company limited by shares,
+is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60)
+with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom.
+Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority
+under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
+Amazon Payments is a trading name of Amazon Payments UK Lim</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 12:05:03 +0000</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Airline discounts and $100 off registration. Available for a limited
+ time</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-20/7z4slz6/6793898954/h/insOo6D5kr2g-YQAHmot70JWv4JNrnk-FJT9rhAtCXc)
+[Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4slz9/6793898954/h/insOo6D5kr2g-YQAHmot70JWv4JNrnk-FJT9rhAtCXc)
+We want you there—so we made it easier
+Your travel plans start here, with exclusive discounts to help make your trip to Seattle more affordable.
+Register now to get the early-bird rate, and join us in Seattle from September 22 to 24. Seats are limited, secure yours today!
+[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4slz9/6793898954/h/insOo6D5kr2g-YQAHmot70JWv4JNrnk-FJT9rhAtCXc)
+"Attending Amazon Accelerate for the first time has been an amazing experience! I feel inspired and more confident in my ability to grow my business with Amazon."
+2025 attendee
+Save on your flight to Seattle
+We’ve partnered with major airlines to offer exclusive discounts on flights to and from Seattle-Tacoma International Airport (SEA).
+[A checkmark icon]
+Alaska Airlines: ~7% off the published price of select fares | Code: ECMQ023 | Valid Sept 17–29
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 28 Jul 2026 08:56:50 +0000</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Your information is verified – Start selling on Amazon now</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Dear Seller,
+Good news. Your Selling on Amazon payment account has been activated. We will get in touch with you if we need more information.
+ For any assistance relating to Selling on Amazon or other Amazon services, you can search our help pages or contact Seller Support/Selling Partner Support.
+Happy Selling.
+Amazon Payments
+ Please Note: this email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions, visit: Seller Central
+ To change your email preferences, visit: Notification Preferences
+ Copyright 2026 Amazon, Inc or its affiliates. All rights reserved.
+ Amazon Payments UK Limited, a private company limited by shares,
+is a company registered in England and Wales (registration number 11049457; VAT number: GB295 7604 60)
+with its registered office at 1 Principal Place, Worship St, London, EC2A 2FA, United Kingdom.
+Amazon Payments UK Limited is authorised by the UK Financial Conduct Authority
+under the Payment Services Regulations 2017 (reference number 799814) for the provision of payment services.
+Amazon Payments is a trading name of Amazon Payments UK Lim</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Thu, 23 Jul 2026 17:52:32 +0000</t>
+          <t>Tue, 28 Jul 2026 14:32:02 +0000</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -15085,11 +15085,60 @@
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>Get faster, personalized support with Seller Assistant</t>
+          <t>Add WhatsApp to your notification preferences</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr"/>
       <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Stay connected with account updates on WhatsApp—opt in today to get started
+ Hello,
+ We're excited to share a new communication channel for your Amazon US selling account. You can now choose to receive important updates, notifications, and support via WhatsApp , giving you more flexibility in how you stay informed.
+ What this means for you
+ WhatsApp is now available as an additional channel for receiving alerts about your Amazon US selling account. This is entirely optional — you won't receive any WhatsApp messages unless you choose to opt in. You'll continue to use Seller Central as the primary way to manage your orders and account.
+ Update preferences
+ How to opt in If you'd like to receive notifications via WhatsApp, follow these steps:
+- Visit the Notification Preferences page in Seller Central
+- Navigate to the WhatsApp tab
+- Add your mobile phone number and complete the verification process Once verified, you'll begin receiving notifications to that number. You can update your preferences at any time, and enabling WhatsApp will not affect your other communication channels with Amazon Seller Services.
+ If you opt in and later change your mind, you can opt out at any time b</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 23 Jul 2026 17:52:32 +0000</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>Get faster, personalized support with Seller Assistant</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr"/>
+      <c r="H284" s="2" t="inlineStr">
         <is>
           <t>96
  When you click Get help and resources, you’ll be directed to Seller Assistant, our AI-powered assistant.
@@ -15101,39 +15150,39 @@
         </is>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" s="2" t="inlineStr">
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B284" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D284" s="2" t="inlineStr">
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 05:44:42 +0000</t>
         </is>
       </c>
-      <c r="E284" s="2" t="inlineStr">
+      <c r="E285" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F284" s="2" t="inlineStr">
+      <c r="F285" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">【重要】西班牙VAT通知期延期指南。税号激活用时最长达37周，请立即行动以免影响销售 </t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr"/>
-      <c r="H284" s="2" t="inlineStr">
+      <c r="G285" s="2" t="inlineStr"/>
+      <c r="H285" s="2" t="inlineStr">
         <is>
           <t>西班牙延期政策更新：已过通知期也可发起申请
 			尊敬的 深圳市微海众信科技有限公司,
@@ -15169,39 +15218,39 @@
         </is>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" s="2" t="inlineStr">
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B285" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C285" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D285" s="2" t="inlineStr">
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 15:32:18 +0000</t>
         </is>
       </c>
-      <c r="E285" s="2" t="inlineStr">
+      <c r="E286" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F285" s="2" t="inlineStr">
+      <c r="F286" s="2" t="inlineStr">
         <is>
           <t>Accelerate 2026: Sessions designed for where you are and where you’re going</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr"/>
-      <c r="H285" s="2" t="inlineStr">
+      <c r="G286" s="2" t="inlineStr"/>
+      <c r="H286" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1pf/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1pj/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
@@ -15213,39 +15262,39 @@
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="2" t="inlineStr">
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B286" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C286" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D286" s="2" t="inlineStr">
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 15:11:01 +0000</t>
         </is>
       </c>
-      <c r="E286" s="2" t="inlineStr">
+      <c r="E287" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F286" s="2" t="inlineStr">
+      <c r="F287" s="2" t="inlineStr">
         <is>
           <t>Your Accelerate 2026 session catalog is now live</t>
         </is>
       </c>
-      <c r="G286" s="2" t="inlineStr"/>
-      <c r="H286" s="2" t="inlineStr">
+      <c r="G287" s="2" t="inlineStr"/>
+      <c r="H287" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1s7/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1sb/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
@@ -15257,40 +15306,40 @@
         </is>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="2" t="inlineStr">
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B287" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C287" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D287" s="2" t="inlineStr">
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Jul 2026 03:21:27 +0000</t>
         </is>
       </c>
-      <c r="E287" s="2" t="inlineStr">
+      <c r="E288" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F287" s="2" t="inlineStr">
+      <c r="F288" s="2" t="inlineStr">
         <is>
           <t>[Amazon.co.uk] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr"/>
-      <c r="H287" s="2" t="inlineStr">
+      <c r="G288" s="2" t="inlineStr"/>
+      <c r="H288" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.co.uk] One or More of Your Amazon Listings Have Been Search Suppressed
